--- a/artfynd/A 2256-2025 artfynd.xlsx
+++ b/artfynd/A 2256-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2552228</v>
+        <v>137516289</v>
       </c>
       <c r="B3" t="n">
-        <v>99049</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219794</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549441</v>
+        <v>550705</v>
       </c>
       <c r="R3" t="n">
-        <v>7395630</v>
+        <v>7394042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera 100 tals</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,42 +879,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Via Annika Rastén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2552228</t>
+          <t>https://artportalen.se/Sighting/137516289</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2634889</v>
+        <v>137516290</v>
       </c>
       <c r="B4" t="n">
-        <v>99017</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,34 +918,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549441</v>
+        <v>550869</v>
       </c>
       <c r="R4" t="n">
-        <v>7395630</v>
+        <v>7393983</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +976,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>100 tals</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,42 +995,38 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Via Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2634889</t>
+          <t>https://artportalen.se/Sighting/137516290</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2463890</v>
+        <v>137516296</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,34 +1034,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549441</v>
+        <v>549193</v>
       </c>
       <c r="R5" t="n">
-        <v>7395630</v>
+        <v>7395884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>100 tals</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,84 +1113,70 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Maj-Lis Granström, Mats G Nettelbladt, Ann-mari Sundkvist</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2463890</t>
+          <t>https://artportalen.se/Sighting/137516296</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104657310</v>
+        <v>2552228</v>
       </c>
       <c r="B6" t="n">
-        <v>98050</v>
+        <v>99049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222112</v>
+        <v>219794</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550173</v>
+        <v>549441</v>
       </c>
       <c r="R6" t="n">
-        <v>7394559</v>
+        <v>7395630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,12 +1203,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,79 +1219,75 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657310</t>
+          <t>https://artportalen.se/Sighting/2552228</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104657311</v>
+        <v>2634889</v>
       </c>
       <c r="B7" t="n">
-        <v>98050</v>
+        <v>99017</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222112</v>
+        <v>219795</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550097</v>
+        <v>549441</v>
       </c>
       <c r="R7" t="n">
-        <v>7394684</v>
+        <v>7395630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,12 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,79 +1330,79 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657311</t>
+          <t>https://artportalen.se/Sighting/2634889</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104657313</v>
+        <v>137516294</v>
       </c>
       <c r="B8" t="n">
-        <v>98050</v>
+        <v>99334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222112</v>
+        <v>219795</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550060</v>
+        <v>550180</v>
       </c>
       <c r="R8" t="n">
-        <v>7394762</v>
+        <v>7394573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,12 +1429,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,75 +1449,70 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657313</t>
+          <t>https://artportalen.se/Sighting/137516294</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104657314</v>
+        <v>137516295</v>
       </c>
       <c r="B9" t="n">
-        <v>98050</v>
+        <v>99334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222112</v>
+        <v>219795</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550085</v>
+        <v>549545</v>
       </c>
       <c r="R9" t="n">
-        <v>7394709</v>
+        <v>7395517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,12 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,75 +1559,66 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657314</t>
+          <t>https://artportalen.se/Sighting/137516295</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104657315</v>
+        <v>2463890</v>
       </c>
       <c r="B10" t="n">
-        <v>98050</v>
+        <v>99022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222112</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550096</v>
+        <v>549441</v>
       </c>
       <c r="R10" t="n">
-        <v>7394713</v>
+        <v>7395630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,12 +1645,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,35 +1661,40 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Maj-Lis Granström, Mats G Nettelbladt, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657315</t>
+          <t>https://artportalen.se/Sighting/2463890</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5988013</v>
+        <v>137516286</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,30 +1702,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549441</v>
+        <v>550689</v>
       </c>
       <c r="R11" t="n">
-        <v>7395630</v>
+        <v>7394050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,12 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,40 +1776,35 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Nathalie Edwards</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5988013</t>
+          <t>https://artportalen.se/Sighting/137516286</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135107148</v>
+        <v>137516288</v>
       </c>
       <c r="B12" t="n">
-        <v>99189</v>
+        <v>99457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,45 +1812,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Merkenes, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549464</v>
+        <v>550691</v>
       </c>
       <c r="R12" t="n">
-        <v>7395597</v>
+        <v>7394050</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,12 +1870,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,61 +1884,64 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Otto Bylén Claesson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Otto Bylén Claesson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Nathalie Edwards</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135107148</t>
+          <t>https://artportalen.se/Sighting/137516288</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104657299</v>
+        <v>104657310</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>98050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>222112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1961,14 +1951,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553184</v>
+        <v>550173</v>
       </c>
       <c r="R13" t="n">
-        <v>7391496</v>
+        <v>7394559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,51 +2020,60 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657299</t>
+          <t>https://artportalen.se/Sighting/104657310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2463889</v>
+        <v>104657311</v>
       </c>
       <c r="B14" t="n">
-        <v>99022</v>
+        <v>98050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>222112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandviken, strax V om, artrik vägslänt, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553684</v>
+        <v>550097</v>
       </c>
       <c r="R14" t="n">
-        <v>7390563</v>
+        <v>7394684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,12 +2100,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,67 +2116,62 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2463889</t>
+          <t>https://artportalen.se/Sighting/104657311</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104657300</v>
+        <v>104657313</v>
       </c>
       <c r="B15" t="n">
-        <v>97982</v>
+        <v>98050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222424</v>
+        <v>222112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2187,14 +2181,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553178</v>
+        <v>550060</v>
       </c>
       <c r="R15" t="n">
-        <v>7391506</v>
+        <v>7394762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,43 +2250,43 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657300</t>
+          <t>https://artportalen.se/Sighting/104657313</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104657301</v>
+        <v>104657314</v>
       </c>
       <c r="B16" t="n">
-        <v>97982</v>
+        <v>98050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222424</v>
+        <v>222112</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2302,14 +2296,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553177</v>
+        <v>550085</v>
       </c>
       <c r="R16" t="n">
-        <v>7391505</v>
+        <v>7394709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,43 +2365,43 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657301</t>
+          <t>https://artportalen.se/Sighting/104657314</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104657302</v>
+        <v>104657315</v>
       </c>
       <c r="B17" t="n">
-        <v>97982</v>
+        <v>98050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222424</v>
+        <v>222112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2417,14 +2411,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553180</v>
+        <v>550096</v>
       </c>
       <c r="R17" t="n">
-        <v>7391498</v>
+        <v>7394713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,60 +2480,47 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657302</t>
+          <t>https://artportalen.se/Sighting/104657315</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104657309</v>
+        <v>5988013</v>
       </c>
       <c r="B18" t="n">
-        <v>98049</v>
+        <v>99038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>164</v>
+        <v>223597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordlåsbräken</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Botrychium boreale</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Milde</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551384</v>
+        <v>549441</v>
       </c>
       <c r="R18" t="n">
-        <v>7393787</v>
+        <v>7395630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2547,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,81 +2563,83 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657309</t>
+          <t>https://artportalen.se/Sighting/5988013</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102038448</v>
+        <v>135107148</v>
       </c>
       <c r="B19" t="n">
-        <v>57791</v>
+        <v>99189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102620</v>
+        <v>223597</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandviken 965, Arjeplog, Pi lm</t>
+          <t>Merkenes, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552520</v>
+        <v>549464</v>
       </c>
       <c r="R19" t="n">
-        <v>7392505</v>
+        <v>7395597</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2683,22 +2666,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19:52</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>19:52</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,30 +2680,31 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Otto Bylén Claesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Otto Bylén Claesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102038448</t>
+          <t>https://artportalen.se/Sighting/135107148</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80435343</v>
+        <v>104657299</v>
       </c>
       <c r="B20" t="n">
         <v>99035</v>
@@ -2758,21 +2732,26 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väg 95, 2 km V Sandviken, Pi lm</t>
+          <t>Vouggatjålme, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552991</v>
+        <v>553184</v>
       </c>
       <c r="R20" t="n">
-        <v>7391874</v>
+        <v>7391496</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,12 +2778,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,34 +2792,37 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80435343</t>
+          <t>https://artportalen.se/Sighting/104657299</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104657317</v>
+        <v>137515388</v>
       </c>
       <c r="B21" t="n">
-        <v>99035</v>
+        <v>99437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,43 +2830,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555155</v>
+        <v>553993</v>
       </c>
       <c r="R21" t="n">
-        <v>7389117</v>
+        <v>7390238</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,12 +2892,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,37 +2911,38 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657317</t>
+          <t>https://artportalen.se/Sighting/137515388</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2552215</v>
+        <v>137515390</v>
       </c>
       <c r="B22" t="n">
-        <v>99049</v>
+        <v>99437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,37 +2950,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219794</v>
+        <v>219811</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandviken, Silvervägen, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554698</v>
+        <v>553995</v>
       </c>
       <c r="R22" t="n">
-        <v>7389785</v>
+        <v>7390236</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3017,12 +3012,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Cirka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,42 +3031,38 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2552215</t>
+          <t>https://artportalen.se/Sighting/137515390</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104657296</v>
+        <v>2463889</v>
       </c>
       <c r="B23" t="n">
-        <v>99017</v>
+        <v>99022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,43 +3070,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219795</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken, strax V om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555305</v>
+        <v>553684</v>
       </c>
       <c r="R23" t="n">
-        <v>7387598</v>
+        <v>7390563</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3137,12 +3124,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,35 +3140,40 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657296</t>
+          <t>https://artportalen.se/Sighting/2463889</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104657298</v>
+        <v>104657300</v>
       </c>
       <c r="B24" t="n">
-        <v>99017</v>
+        <v>97982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,21 +3181,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219795</v>
+        <v>222424</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fjällummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lycopodium alpinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3222,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555105</v>
+        <v>553178</v>
       </c>
       <c r="R24" t="n">
-        <v>7388477</v>
+        <v>7391506</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,16 +3279,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657298</t>
+          <t>https://artportalen.se/Sighting/104657300</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104657304</v>
+        <v>104657301</v>
       </c>
       <c r="B25" t="n">
-        <v>99120</v>
+        <v>97982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,26 +3296,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219811</v>
+        <v>222424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fjällummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium alpinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3337,10 +3329,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555301</v>
+        <v>553177</v>
       </c>
       <c r="R25" t="n">
-        <v>7387612</v>
+        <v>7391505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,16 +3394,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657304</t>
+          <t>https://artportalen.se/Sighting/104657301</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104657320</v>
+        <v>104657302</v>
       </c>
       <c r="B26" t="n">
-        <v>99120</v>
+        <v>97982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3419,26 +3411,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219811</v>
+        <v>222424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fjällummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium alpinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3452,10 +3444,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555289</v>
+        <v>553180</v>
       </c>
       <c r="R26" t="n">
-        <v>7387631</v>
+        <v>7391498</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,54 +3509,63 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657320</t>
+          <t>https://artportalen.se/Sighting/104657302</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2463597</v>
+        <v>104657309</v>
       </c>
       <c r="B27" t="n">
-        <v>99022</v>
+        <v>98049</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>164</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Milde</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandviken, Silvervägen, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>554380</v>
+        <v>551384</v>
       </c>
       <c r="R27" t="n">
-        <v>7389914</v>
+        <v>7393787</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3588,12 +3589,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,62 +3605,57 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2463597</t>
+          <t>https://artportalen.se/Sighting/104657309</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104657293</v>
+        <v>102038448</v>
       </c>
       <c r="B28" t="n">
-        <v>99022</v>
+        <v>57791</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>102620</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3667,24 +3663,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken 965, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555298</v>
+        <v>552520</v>
       </c>
       <c r="R28" t="n">
-        <v>7387615</v>
+        <v>7392505</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3708,12 +3706,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2022-07-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2022-07-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3728,31 +3736,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657293</t>
+          <t>https://artportalen.se/Sighting/102038448</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104657321</v>
+        <v>80435343</v>
       </c>
       <c r="B29" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,43 +3764,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Väg 95, 2 km V Sandviken, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>554581</v>
+        <v>552991</v>
       </c>
       <c r="R29" t="n">
-        <v>7389832</v>
+        <v>7391874</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3823,12 +3822,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3837,37 +3836,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657321</t>
+          <t>https://artportalen.se/Sighting/80435343</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2634914</v>
+        <v>137516291</v>
       </c>
       <c r="B30" t="n">
-        <v>99017</v>
+        <v>99352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,37 +3871,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558709</v>
+        <v>551366</v>
       </c>
       <c r="R30" t="n">
-        <v>7383327</v>
+        <v>7393790</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3929,12 +3929,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>100 tals</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,42 +3948,38 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>extremrikkärr</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Via Annika Rastén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2634914</t>
+          <t>https://artportalen.se/Sighting/137516291</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4400318</v>
+        <v>137516293</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>99352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3986,37 +3987,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558709</v>
+        <v>552423</v>
       </c>
       <c r="R31" t="n">
-        <v>7383327</v>
+        <v>7392698</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4040,12 +4045,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>100 tals</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4056,40 +4066,35 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>extremrikkärr</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4400318</t>
+          <t>https://artportalen.se/Sighting/137516293</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4898865</v>
+        <v>137516292</v>
       </c>
       <c r="B32" t="n">
-        <v>100143</v>
+        <v>99437</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,34 +4102,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222467</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vuoggatjålmjaure SV, Tjålmevaratj S, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558757</v>
+        <v>552389</v>
       </c>
       <c r="R32" t="n">
-        <v>7383211</v>
+        <v>7392782</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4151,12 +4160,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2012-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2012-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,29 +4176,3445 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>sluttningsmyr</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137516292</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>104657317</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555155</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7389117</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657317</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137515391</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99352</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>554737</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7389766</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515391</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137515393</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99352</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>554871</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7389674</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515393</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137515400</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99352</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>555135</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7389160</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515400</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137515403</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99352</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>555104</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7388452</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515403</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137515406</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99352</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>555289</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7387599</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515406</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2552215</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99049</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219794</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sumpnycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sandviken, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>554698</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7389785</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2552215</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>104657296</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>555305</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7387598</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657296</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>104657298</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>555105</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7388477</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657298</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137515396</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99334</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>554711</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7389794</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515396</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>104657304</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>555301</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7387612</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657304</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>104657320</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>555289</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7387631</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657320</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137515392</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99437</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>554728</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7389767</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515392</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137515427</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99437</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>555308</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7387611</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Mittpunkt. Förekommer längs en sträcka om ca</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515427</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2463597</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sandviken, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>554380</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7389914</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2463597</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>104657293</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>555298</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7387615</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657293</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>104657321</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>554581</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7389832</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657321</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137515404</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99339</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>555103</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7388453</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515404</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137515424</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99339</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>555549</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7387291</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Cirka. Mittpunkt på en sträcka av ca 500 m</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515424</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137515425</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99339</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>555356</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7387518</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mittpunkt på en sträcka av ca 50 m</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515425</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137515402</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99457</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>555102</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7388453</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Cirka</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515402</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137515426</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99457</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>555319</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7387580</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Weronika Hjelm Olsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515426</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137515405</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>555297</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7387604</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Växer högt upp i bankslänt innanför vägräcket</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Via Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515405</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137515413</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>555349</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7387510</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Växer högt upp i bankslänt innanför vägräcket</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Via Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515413</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137515417</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>555372</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7387470</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växer högt upp i bankslänt innanför vägräcket</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Via Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515417</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137515418</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>555382</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7387459</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Växer högt upp i bankslänt innanför vägräcket</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Via Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515418</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137515419</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>555412</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7387430</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Växer högt upp i bankslänt innanför vägräcket</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Via Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137515419</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2634914</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>558709</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7383327</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>extremrikkärr</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634914</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4400318</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>558709</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7383327</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>extremrikkärr</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4400318</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4898865</v>
+      </c>
+      <c r="B62" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vuoggatjålmjaure SV, Tjålmevaratj S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>558757</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7383211</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2012-07-21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2012-07-21</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>sluttningsmyr</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
           <t>Mats G Nettelbladt</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>Mats G Nettelbladt, Ann-mari Sundkvist</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
+      <c r="AY62" t="inlineStr">
         <is>
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/4898865</t>
         </is>
@@ -4228,6 +7653,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2256-2025 artfynd.xlsx
+++ b/artfynd/A 2256-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137516289</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137516290</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>137516296</v>
       </c>
       <c r="B5" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137516294</v>
       </c>
       <c r="B8" t="n">
-        <v>99334</v>
+        <v>99337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>137516295</v>
       </c>
       <c r="B9" t="n">
-        <v>99334</v>
+        <v>99337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>137516286</v>
       </c>
       <c r="B11" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137516288</v>
       </c>
       <c r="B12" t="n">
-        <v>99457</v>
+        <v>99460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137515388</v>
       </c>
       <c r="B21" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137515390</v>
       </c>
       <c r="B22" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>137516291</v>
       </c>
       <c r="B30" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>137516293</v>
       </c>
       <c r="B31" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>137516292</v>
       </c>
       <c r="B32" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>137515391</v>
       </c>
       <c r="B34" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>137515393</v>
       </c>
       <c r="B35" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>137515400</v>
       </c>
       <c r="B36" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>137515403</v>
       </c>
       <c r="B37" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>137515406</v>
       </c>
       <c r="B38" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>137515396</v>
       </c>
       <c r="B42" t="n">
-        <v>99334</v>
+        <v>99337</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>137515392</v>
       </c>
       <c r="B45" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>137515427</v>
       </c>
       <c r="B46" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>137515404</v>
       </c>
       <c r="B50" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137515424</v>
       </c>
       <c r="B51" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137515425</v>
       </c>
       <c r="B52" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>137515402</v>
       </c>
       <c r="B53" t="n">
-        <v>99457</v>
+        <v>99460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>137515426</v>
       </c>
       <c r="B54" t="n">
-        <v>99457</v>
+        <v>99460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>137515405</v>
       </c>
       <c r="B55" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>137515413</v>
       </c>
       <c r="B56" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>137515417</v>
       </c>
       <c r="B57" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>137515418</v>
       </c>
       <c r="B58" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>137515419</v>
       </c>
       <c r="B59" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
